--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,22 +3479,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G62" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI65"/>
+  <dimension ref="A1:AI64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46097.625</v>
+        <v>46097.64583333334</v>
       </c>
     </row>
     <row r="27">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46097.64583333334</v>
+        <v>46097.65625</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46097.65625</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="38">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="40">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="46">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6211,27 +6211,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.71875</v>
       </c>
     </row>
     <row r="50">
@@ -6330,27 +6330,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46097.71875</v>
+        <v>46097.75</v>
       </c>
     </row>
     <row r="51">
@@ -6449,27 +6449,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46097.75</v>
+        <v>46097.79166666666</v>
       </c>
     </row>
     <row r="52">
@@ -6568,27 +6568,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46097.79166666666</v>
+        <v>46097.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46097.83333333334</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="54">
@@ -6925,27 +6925,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.875</v>
       </c>
     </row>
     <row r="56">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7996,27 +7996,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8106,125 +8106,6 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI64"/>
+  <dimension ref="A1:AI67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,22 +1575,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46097.64583333334</v>
+        <v>46097.625</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46097.64583333334</v>
+        <v>46097.625</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46097.65625</v>
+        <v>46097.625</v>
       </c>
     </row>
     <row r="29">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.64583333334</v>
       </c>
     </row>
     <row r="30">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.64583333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.65625</v>
       </c>
     </row>
     <row r="32">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="38">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="39">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -5140,27 +5140,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="41">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="42">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="46">
@@ -5854,27 +5854,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="47">
@@ -5973,27 +5973,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="48">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6211,27 +6211,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46097.71875</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="50">
@@ -6330,27 +6330,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
-        <v>46097.75</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="51">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46097.79166666666</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="52">
@@ -6568,27 +6568,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46097.83333333334</v>
+        <v>46097.71875</v>
       </c>
     </row>
     <row r="53">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.75</v>
       </c>
     </row>
     <row r="54">
@@ -6806,27 +6806,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.79166666666</v>
       </c>
     </row>
     <row r="55">
@@ -6925,27 +6925,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>46097.875</v>
+        <v>46097.83333333334</v>
       </c>
     </row>
     <row r="56">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
-        <v>46097.875</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="57">
@@ -7163,27 +7163,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
-        <v>46097.875</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="58">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,22 +7763,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7996,116 +7996,473 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>El Bayadh</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3" t="n">
+        <v>46097.875</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3" t="n">
+        <v>46097.875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" s="3" t="n">
+        <v>46097.875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Racing United</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" s="3" t="n">
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI67"/>
+  <dimension ref="A1:BI67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,125 +488,255 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Goals_H_2T</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Goals_A_2T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cantos_H</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Cantos_A</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_FT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_FT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_FT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_HT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over25</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under25</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over45</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under45</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_A</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_75</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_85</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_95</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_105</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_over_115</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_75</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_85</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_95</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_105</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_under_115</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>odds_corners_2</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_over05</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_over15</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under05</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under15</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>odds_2nd_half_under25</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -653,23 +783,23 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
@@ -727,7 +857,85 @@
       <c r="AH2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="3" t="n">
         <v>46097.25</v>
       </c>
     </row>
@@ -772,23 +980,23 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
@@ -846,7 +1054,85 @@
       <c r="AH3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" s="3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="3" t="n">
         <v>46097.29166666666</v>
       </c>
     </row>
@@ -891,23 +1177,23 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
@@ -965,7 +1251,85 @@
       <c r="AH4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" s="3" t="n">
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="3" t="n">
         <v>46097.29166666666</v>
       </c>
     </row>
@@ -1010,23 +1374,23 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -1084,7 +1448,85 @@
       <c r="AH5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" s="3" t="n">
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="3" t="n">
         <v>46097.3125</v>
       </c>
     </row>
@@ -1129,23 +1571,23 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
@@ -1203,7 +1645,85 @@
       <c r="AH6" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" s="3" t="n">
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="3" t="n">
         <v>46097.375</v>
       </c>
     </row>
@@ -1248,23 +1768,23 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -1322,7 +1842,85 @@
       <c r="AH7" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" s="3" t="n">
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="3" t="n">
         <v>46097.39583333334</v>
       </c>
     </row>
@@ -1367,23 +1965,23 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1441,7 +2039,85 @@
       <c r="AH8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" s="3" t="n">
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="3" t="n">
         <v>46097.41666666666</v>
       </c>
     </row>
@@ -1486,23 +2162,23 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1560,7 +2236,85 @@
       <c r="AH9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" s="3" t="n">
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="3" t="n">
         <v>46097.41666666666</v>
       </c>
     </row>
@@ -1605,23 +2359,23 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1679,7 +2433,85 @@
       <c r="AH10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" s="3" t="n">
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3" t="n">
         <v>46097.45833333334</v>
       </c>
     </row>
@@ -1724,23 +2556,23 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1798,7 +2630,85 @@
       <c r="AH11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="3" t="n">
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="3" t="n">
         <v>46097.45833333334</v>
       </c>
     </row>
@@ -1843,23 +2753,23 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1917,7 +2827,85 @@
       <c r="AH12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="3" t="n">
         <v>46097.5</v>
       </c>
     </row>
@@ -1962,23 +2950,23 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
@@ -2036,7 +3024,85 @@
       <c r="AH13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" s="3" t="n">
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="3" t="n">
         <v>46097.54166666666</v>
       </c>
     </row>
@@ -2081,32 +3147,32 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>1.67</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>3.5</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>5.68</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
@@ -2155,7 +3221,85 @@
       <c r="AH14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="n">
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="3" t="n">
         <v>46097.54166666666</v>
       </c>
     </row>
@@ -2200,31 +3344,31 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2274,7 +3418,85 @@
       <c r="AH15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" s="3" t="n">
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
         <v>46097.5625</v>
       </c>
     </row>
@@ -2319,23 +3541,23 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -2393,7 +3615,85 @@
       <c r="AH16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="3" t="n">
         <v>46097.58333333334</v>
       </c>
     </row>
@@ -2438,23 +3738,23 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
@@ -2512,7 +3812,85 @@
       <c r="AH17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="3" t="n">
         <v>46097.58333333334</v>
       </c>
     </row>
@@ -2557,32 +3935,32 @@
       <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="P18" t="n">
         <v>7.14</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
         <v>4.45</v>
       </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
         <v>1.41</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
@@ -2631,7 +4009,85 @@
       <c r="AH18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="3" t="n">
         <v>46097.58333333334</v>
       </c>
     </row>
@@ -2676,23 +4132,23 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
@@ -2750,7 +4206,85 @@
       <c r="AH19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="3" t="n">
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="3" t="n">
         <v>46097.58333333334</v>
       </c>
     </row>
@@ -2795,32 +4329,32 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="P20" t="n">
         <v>1.64</v>
       </c>
-      <c r="M20" t="n">
+      <c r="Q20" t="n">
         <v>4.3</v>
       </c>
-      <c r="N20" t="n">
+      <c r="R20" t="n">
         <v>4.28</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
@@ -2869,7 +4403,85 @@
       <c r="AH20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="n">
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="3" t="n">
         <v>46097.58333333334</v>
       </c>
     </row>
@@ -2914,23 +4526,23 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
@@ -2988,7 +4600,85 @@
       <c r="AH21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" s="3" t="n">
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="3" t="n">
         <v>46097.60416666666</v>
       </c>
     </row>
@@ -3033,23 +4723,23 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +4797,85 @@
       <c r="AH22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="n">
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="3" t="n">
         <v>46097.60416666666</v>
       </c>
     </row>
@@ -3152,23 +4920,23 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
@@ -3226,7 +4994,85 @@
       <c r="AH23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" s="3" t="n">
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" s="3" t="n">
         <v>46097.625</v>
       </c>
     </row>
@@ -3271,23 +5117,23 @@
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
@@ -3345,7 +5191,85 @@
       <c r="AH24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" s="3" t="n">
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" s="3" t="n">
         <v>46097.625</v>
       </c>
     </row>
@@ -3390,23 +5314,23 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
@@ -3464,7 +5388,85 @@
       <c r="AH25" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" s="3" t="n">
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" s="3" t="n">
         <v>46097.625</v>
       </c>
     </row>
@@ -3509,32 +5511,32 @@
       <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="P26" t="n">
         <v>1.87</v>
       </c>
-      <c r="M26" t="n">
+      <c r="Q26" t="n">
         <v>3.6</v>
       </c>
-      <c r="N26" t="n">
+      <c r="R26" t="n">
         <v>3.55</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
@@ -3583,7 +5585,85 @@
       <c r="AH26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" s="3" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" s="3" t="n">
         <v>46097.625</v>
       </c>
     </row>
@@ -3628,23 +5708,23 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
@@ -3702,7 +5782,85 @@
       <c r="AH27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" s="3" t="n">
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" s="3" t="n">
         <v>46097.625</v>
       </c>
     </row>
@@ -3747,23 +5905,23 @@
       <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
@@ -3821,7 +5979,85 @@
       <c r="AH28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" s="3" t="n">
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" s="3" t="n">
         <v>46097.625</v>
       </c>
     </row>
@@ -3866,23 +6102,23 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -3940,7 +6176,85 @@
       <c r="AH29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" s="3" t="n">
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3" t="n">
         <v>46097.64583333334</v>
       </c>
     </row>
@@ -3985,23 +6299,23 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
@@ -4059,7 +6373,85 @@
       <c r="AH30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" s="3" t="n">
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="3" t="n">
         <v>46097.64583333334</v>
       </c>
     </row>
@@ -4104,23 +6496,23 @@
       <c r="J31" t="n">
         <v>0</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -4178,7 +6570,85 @@
       <c r="AH31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" s="3" t="n">
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3" t="n">
         <v>46097.65625</v>
       </c>
     </row>
@@ -4223,23 +6693,23 @@
       <c r="J32" t="n">
         <v>0</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
@@ -4297,7 +6767,85 @@
       <c r="AH32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="n">
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -4342,23 +6890,23 @@
       <c r="J33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -4416,7 +6964,85 @@
       <c r="AH33" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" s="3" t="n">
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -4461,23 +7087,23 @@
       <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
@@ -4535,7 +7161,85 @@
       <c r="AH34" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" s="3" t="n">
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -4580,23 +7284,23 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
@@ -4654,7 +7358,85 @@
       <c r="AH35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" s="3" t="n">
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -4699,23 +7481,23 @@
       <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
@@ -4773,7 +7555,85 @@
       <c r="AH36" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" s="3" t="n">
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -4818,23 +7678,23 @@
       <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
@@ -4892,7 +7752,85 @@
       <c r="AH37" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" s="3" t="n">
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -4937,23 +7875,23 @@
       <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
@@ -5011,7 +7949,85 @@
       <c r="AH38" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" s="3" t="n">
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -5056,23 +8072,23 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
@@ -5130,7 +8146,85 @@
       <c r="AH39" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" s="3" t="n">
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" s="3" t="n">
         <v>46097.66666666666</v>
       </c>
     </row>
@@ -5175,23 +8269,23 @@
       <c r="J40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
@@ -5249,7 +8343,85 @@
       <c r="AH40" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" s="3" t="n">
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" s="3" t="n">
         <v>46097.6875</v>
       </c>
     </row>
@@ -5294,23 +8466,23 @@
       <c r="J41" t="n">
         <v>0</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
@@ -5368,7 +8540,85 @@
       <c r="AH41" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" s="3" t="n">
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="3" t="n">
         <v>46097.6875</v>
       </c>
     </row>
@@ -5413,23 +8663,23 @@
       <c r="J42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
@@ -5487,7 +8737,85 @@
       <c r="AH42" t="n">
         <v>0</v>
       </c>
-      <c r="AI42" s="3" t="n">
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3" t="n">
         <v>46097.69791666666</v>
       </c>
     </row>
@@ -5532,23 +8860,23 @@
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
@@ -5606,7 +8934,85 @@
       <c r="AH43" t="n">
         <v>0</v>
       </c>
-      <c r="AI43" s="3" t="n">
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="3" t="n">
         <v>46097.69791666666</v>
       </c>
     </row>
@@ -5651,23 +9057,23 @@
       <c r="J44" t="n">
         <v>0</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
@@ -5725,7 +9131,85 @@
       <c r="AH44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" s="3" t="n">
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
         <v>46097.69791666666</v>
       </c>
     </row>
@@ -5770,32 +9254,32 @@
       <c r="J45" t="n">
         <v>0</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="P45" t="n">
         <v>4.04</v>
       </c>
-      <c r="M45" t="n">
+      <c r="Q45" t="n">
         <v>3.64</v>
       </c>
-      <c r="N45" t="n">
+      <c r="R45" t="n">
         <v>2.03</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
@@ -5821,30 +9305,108 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.89</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AF45" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
       <c r="AG45" t="n">
         <v>0</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" s="3" t="n">
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="3" t="n">
         <v>46097.69791666666</v>
       </c>
     </row>
@@ -5889,23 +9451,23 @@
       <c r="J46" t="n">
         <v>0</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
@@ -5963,7 +9525,85 @@
       <c r="AH46" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" s="3" t="n">
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
         <v>46097.69791666666</v>
       </c>
     </row>
@@ -6008,23 +9648,23 @@
       <c r="J47" t="n">
         <v>0</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
@@ -6082,7 +9722,85 @@
       <c r="AH47" t="n">
         <v>0</v>
       </c>
-      <c r="AI47" s="3" t="n">
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="3" t="n">
         <v>46097.69791666666</v>
       </c>
     </row>
@@ -6127,23 +9845,23 @@
       <c r="J48" t="n">
         <v>0</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
@@ -6201,7 +9919,85 @@
       <c r="AH48" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" s="3" t="n">
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="3" t="n">
         <v>46097.70833333334</v>
       </c>
     </row>
@@ -6246,23 +10042,23 @@
       <c r="J49" t="n">
         <v>0</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
@@ -6320,7 +10116,85 @@
       <c r="AH49" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" s="3" t="n">
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI49" s="3" t="n">
         <v>46097.70833333334</v>
       </c>
     </row>
@@ -6365,32 +10239,32 @@
       <c r="J50" t="n">
         <v>0</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="P50" t="n">
         <v>1.59</v>
       </c>
-      <c r="M50" t="n">
+      <c r="Q50" t="n">
         <v>4.32</v>
       </c>
-      <c r="N50" t="n">
+      <c r="R50" t="n">
         <v>6.55</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
@@ -6416,30 +10290,108 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1.76</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AF50" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
       <c r="AG50" t="n">
         <v>0</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" s="3" t="n">
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI50" s="3" t="n">
         <v>46097.70833333334</v>
       </c>
     </row>
@@ -6484,23 +10436,23 @@
       <c r="J51" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
@@ -6558,7 +10510,85 @@
       <c r="AH51" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" s="3" t="n">
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="3" t="n">
         <v>46097.70833333334</v>
       </c>
     </row>
@@ -6603,23 +10633,23 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
@@ -6677,7 +10707,85 @@
       <c r="AH52" t="n">
         <v>0</v>
       </c>
-      <c r="AI52" s="3" t="n">
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="3" t="n">
         <v>46097.71875</v>
       </c>
     </row>
@@ -6722,23 +10830,23 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
@@ -6796,7 +10904,85 @@
       <c r="AH53" t="n">
         <v>0</v>
       </c>
-      <c r="AI53" s="3" t="n">
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="3" t="n">
         <v>46097.75</v>
       </c>
     </row>
@@ -6841,23 +11027,23 @@
       <c r="J54" t="n">
         <v>0</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
@@ -6915,7 +11101,85 @@
       <c r="AH54" t="n">
         <v>0</v>
       </c>
-      <c r="AI54" s="3" t="n">
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="3" t="n">
         <v>46097.79166666666</v>
       </c>
     </row>
@@ -6960,32 +11224,32 @@
       <c r="J55" t="n">
         <v>0</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="P55" t="n">
         <v>3.02</v>
       </c>
-      <c r="M55" t="n">
+      <c r="Q55" t="n">
         <v>3.25</v>
       </c>
-      <c r="N55" t="n">
+      <c r="R55" t="n">
         <v>2.48</v>
       </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
@@ -7011,30 +11275,108 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AF55" t="n">
         <v>1.68</v>
       </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
       <c r="AG55" t="n">
         <v>0</v>
       </c>
       <c r="AH55" t="n">
         <v>0</v>
       </c>
-      <c r="AI55" s="3" t="n">
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="3" t="n">
         <v>46097.83333333334</v>
       </c>
     </row>
@@ -7079,23 +11421,23 @@
       <c r="J56" t="n">
         <v>0</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
@@ -7153,7 +11495,85 @@
       <c r="AH56" t="n">
         <v>0</v>
       </c>
-      <c r="AI56" s="3" t="n">
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" s="3" t="n">
         <v>46097.85416666666</v>
       </c>
     </row>
@@ -7198,23 +11618,23 @@
       <c r="J57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
@@ -7272,7 +11692,85 @@
       <c r="AH57" t="n">
         <v>0</v>
       </c>
-      <c r="AI57" s="3" t="n">
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="3" t="n">
         <v>46097.85416666666</v>
       </c>
     </row>
@@ -7317,23 +11815,23 @@
       <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
@@ -7391,7 +11889,85 @@
       <c r="AH58" t="n">
         <v>0</v>
       </c>
-      <c r="AI58" s="3" t="n">
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI58" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -7436,23 +12012,23 @@
       <c r="J59" t="n">
         <v>0</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
@@ -7510,7 +12086,85 @@
       <c r="AH59" t="n">
         <v>0</v>
       </c>
-      <c r="AI59" s="3" t="n">
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI59" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -7555,23 +12209,23 @@
       <c r="J60" t="n">
         <v>0</v>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O60" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
@@ -7629,7 +12283,85 @@
       <c r="AH60" t="n">
         <v>0</v>
       </c>
-      <c r="AI60" s="3" t="n">
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI60" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -7674,23 +12406,23 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O61" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
@@ -7748,7 +12480,85 @@
       <c r="AH61" t="n">
         <v>0</v>
       </c>
-      <c r="AI61" s="3" t="n">
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI61" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -7793,32 +12603,32 @@
       <c r="J62" t="n">
         <v>0</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="P62" t="n">
         <v>2.33</v>
       </c>
-      <c r="M62" t="n">
+      <c r="Q62" t="n">
         <v>2.85</v>
       </c>
-      <c r="N62" t="n">
+      <c r="R62" t="n">
         <v>3.13</v>
       </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
@@ -7867,7 +12677,85 @@
       <c r="AH62" t="n">
         <v>0</v>
       </c>
-      <c r="AI62" s="3" t="n">
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI62" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -7912,23 +12800,23 @@
       <c r="J63" t="n">
         <v>0</v>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
@@ -7986,7 +12874,85 @@
       <c r="AH63" t="n">
         <v>0</v>
       </c>
-      <c r="AI63" s="3" t="n">
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI63" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -8031,23 +12997,23 @@
       <c r="J64" t="n">
         <v>0</v>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O64" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -8105,7 +13071,85 @@
       <c r="AH64" t="n">
         <v>0</v>
       </c>
-      <c r="AI64" s="3" t="n">
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI64" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -8150,23 +13194,23 @@
       <c r="J65" t="n">
         <v>0</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
@@ -8224,7 +13268,85 @@
       <c r="AH65" t="n">
         <v>0</v>
       </c>
-      <c r="AI65" s="3" t="n">
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI65" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -8269,23 +13391,23 @@
       <c r="J66" t="n">
         <v>0</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
@@ -8343,7 +13465,85 @@
       <c r="AH66" t="n">
         <v>0</v>
       </c>
-      <c r="AI66" s="3" t="n">
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI66" s="3" t="n">
         <v>46097.875</v>
       </c>
     </row>
@@ -8388,23 +13588,23 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
@@ -8462,7 +13662,85 @@
       <c r="AH67" t="n">
         <v>0</v>
       </c>
-      <c r="AI67" s="3" t="n">
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>7.14</v>
+        <v>1.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.45</v>
+        <v>6.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>7.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.17</v>
+        <v>7.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.4</v>
+        <v>4.45</v>
       </c>
       <c r="R19" t="n">
-        <v>15.5</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.14</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.45</v>
+        <v>6.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI67"/>
+  <dimension ref="A1:BI66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>7.14</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>4.28</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46097.64583333334</v>
+        <v>46097.65625</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46097.65625</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="32">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="40">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="42">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.71875</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46097.71875</v>
+        <v>46097.75</v>
       </c>
     </row>
     <row r="53">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46097.75</v>
+        <v>46097.79166666666</v>
       </c>
     </row>
     <row r="54">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46097.79166666666</v>
+        <v>46097.83333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46097.83333333334</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="56">
@@ -11583,27 +11583,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.875</v>
       </c>
     </row>
     <row r="58">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,203 +13544,6 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI66"/>
+  <dimension ref="A1:BI68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>5.68</v>
+        <v>4.49</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46097.54166666666</v>
+        <v>46097.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>4.34</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46097.5625</v>
+        <v>46097.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46097.58333333334</v>
+        <v>46097.5625</v>
       </c>
     </row>
     <row r="17">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.14</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>4.28</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="R19" t="n">
-        <v>4.28</v>
+        <v>15.5</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46097.60416666666</v>
+        <v>46097.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46097.625</v>
+        <v>46097.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46097.64583333334</v>
+        <v>46097.625</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46097.65625</v>
+        <v>46097.64583333334</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.64583333334</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.65625</v>
       </c>
     </row>
     <row r="33">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="42">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="43">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.04</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="48">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="49">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46097.71875</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46097.75</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46097.79166666666</v>
+        <v>46097.71875</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46097.83333333334</v>
+        <v>46097.75</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.79166666666</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.83333333334</v>
       </c>
     </row>
     <row r="57">
@@ -11583,27 +11583,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46097.875</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46097.875</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="59">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,6 +13544,400 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
+        <v>46097.875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="3" t="n">
+        <v>46097.875</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Racing United</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI68" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI68"/>
+  <dimension ref="A1:BI67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>7.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>4.28</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.14</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46097.64583333334</v>
+        <v>46097.65625</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46097.65625</v>
+        <v>46097.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46097.66666666666</v>
+        <v>46097.6875</v>
       </c>
     </row>
     <row r="41">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46097.6875</v>
+        <v>46097.69791666666</v>
       </c>
     </row>
     <row r="43">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46097.69791666666</v>
+        <v>46097.70833333334</v>
       </c>
     </row>
     <row r="49">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46097.70833333334</v>
+        <v>46097.71875</v>
       </c>
     </row>
     <row r="53">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46097.71875</v>
+        <v>46097.75</v>
       </c>
     </row>
     <row r="54">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46097.75</v>
+        <v>46097.79166666666</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46097.79166666666</v>
+        <v>46097.83333333334</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46097.83333333334</v>
+        <v>46097.85416666666</v>
       </c>
     </row>
     <row r="57">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46097.85416666666</v>
+        <v>46097.875</v>
       </c>
     </row>
     <row r="59">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,203 +13741,6 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI68" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI67"/>
+  <dimension ref="A1:BI59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.14</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>4.28</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>7.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.4</v>
+        <v>4.45</v>
       </c>
       <c r="R21" t="n">
-        <v>15.5</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,1582 +12165,6 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>USM Khenchela</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI60" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Oued Akbou</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>CS Constantine</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI61" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI62" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI63" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>ASO Chlef</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI64" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Deportivo Maipú</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R65" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI65" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Ben Aknoun</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>MB Rouisset</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI66" s="3" t="n">
-        <v>46097.875</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="3" t="n">
         <v>46097.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>7.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>4.28</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="R41" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.32</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>6.55</v>
+        <v>3.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>3.1</v>
+        <v>6.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.14</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>4.28</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>15.5</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="R40" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="R17" t="n">
-        <v>4.28</v>
+        <v>15.5</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>15.5</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,17 +6707,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.04</v>
+        <v>2.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="R17" t="n">
-        <v>15.5</v>
+        <v>4.28</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,17 +6707,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.14</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.45</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,17 +7692,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.17</v>
+        <v>7.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.4</v>
+        <v>4.45</v>
       </c>
       <c r="R18" t="n">
-        <v>15.5</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>7.14</v>
+        <v>1.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.45</v>
+        <v>6.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="R41" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,17 +7692,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="R40" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.32</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>6.55</v>
+        <v>3.1</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.14</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>4.28</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="R21" t="n">
-        <v>4.28</v>
+        <v>15.5</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,17 +7495,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="R41" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2977,124 +2977,124 @@
         <v>4.49</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3568,70 +3568,70 @@
         <v>4.34</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.14</v>
+        <v>1.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>6.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4356,70 +4356,70 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5932,124 +5932,124 @@
         <v>3.55</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,83 +6707,83 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7105,130 +7105,130 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,52 +7383,52 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB35" t="n">
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,134 +7495,134 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,130 +8090,130 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="R40" t="n">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>4.32</v>
       </c>
       <c r="R51" t="n">
-        <v>3.1</v>
+        <v>6.55</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>6.52</v>
+        <v>2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="X14" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
         <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.27</v>
+        <v>1.15</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
         <v>2.05</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AV14" t="n">
         <v>2.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.5</v>
+        <v>1.63</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.31</v>
+        <v>6.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.45</v>
+        <v>8.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB15" t="n">
         <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.15</v>
+        <v>2.27</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AV15" t="n">
         <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.68</v>
+        <v>1.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R16" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="S16" t="n">
         <v>2.7</v>
@@ -3613,7 +3613,7 @@
         <v>4.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
         <v>8.300000000000001</v>
@@ -3622,7 +3622,7 @@
         <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AL16" t="n">
         <v>1.71</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.64</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AL19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM19" t="n">
         <v>1.17</v>
       </c>
-      <c r="AD19" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AN19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>4.57</v>
+        <v>1.85</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="U25" t="n">
-        <v>4.12</v>
+        <v>3.77</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA25" t="n">
         <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BB25" t="n">
         <v>1.17</v>
       </c>
       <c r="BC25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.95</v>
       </c>
-      <c r="BD25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,137 +6707,137 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>6.95</v>
+        <v>1.69</v>
       </c>
       <c r="S32" t="n">
-        <v>1.84</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
         <v>2.55</v>
       </c>
       <c r="U32" t="n">
-        <v>6.5</v>
+        <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="X32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV32" t="n">
         <v>2.48</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,83 +6904,83 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q34" t="n">
         <v>4.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.69</v>
+        <v>3.6</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="T34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW34" t="n">
         <v>2.55</v>
       </c>
-      <c r="U34" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE34" t="n">
+      <c r="AX34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
         <v>2.45</v>
       </c>
-      <c r="AG34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ34" t="n">
+      <c r="BF34" t="n">
         <v>1.46</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN35" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV35" t="n">
         <v>2.8</v>
       </c>
-      <c r="U35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AW35" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="BB35" t="n">
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,67 +8090,67 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>3.36</v>
+        <v>4.19</v>
       </c>
       <c r="S39" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="T39" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U39" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="X39" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK39" t="n">
         <v>1.43</v>
@@ -8159,61 +8159,61 @@
         <v>2.63</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AR39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
         <v>1.61</v>
       </c>
-      <c r="AS39" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.88</v>
+        <v>4.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>3.64</v>
       </c>
       <c r="R45" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31</v>
+        <v>6.52</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="X14" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.45</v>
+        <v>8.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB14" t="n">
         <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.15</v>
+        <v>2.27</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AR14" t="n">
         <v>2.05</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AV14" t="n">
         <v>2.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.68</v>
+        <v>1.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>6.52</v>
+        <v>2.31</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="X15" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB15" t="n">
         <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.27</v>
+        <v>1.15</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AV15" t="n">
         <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.5</v>
+        <v>1.63</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>4.57</v>
+        <v>1.85</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="X19" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>6.6</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN20" t="n">
         <v>1.85</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
         <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>4.68</v>
+        <v>3.55</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,137 +6904,137 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="Q33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W33" t="n">
         <v>4.6</v>
       </c>
-      <c r="R33" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="X33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW33" t="n">
         <v>2.55</v>
       </c>
-      <c r="U33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE33" t="n">
+      <c r="AX33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY33" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF33" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH33" t="n">
+      <c r="AZ33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
         <v>1.47</v>
       </c>
-      <c r="AI33" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,137 +7101,137 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="R34" t="n">
-        <v>3.6</v>
+        <v>6.95</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="T34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN34" t="n">
         <v>2.8</v>
       </c>
-      <c r="U34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
+      <c r="BF34" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.46</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,130 +8090,130 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.04</v>
+        <v>2.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R55" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>6.52</v>
+        <v>2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="X14" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
         <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.27</v>
+        <v>1.15</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
         <v>2.05</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AV14" t="n">
         <v>2.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.5</v>
+        <v>1.63</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>5.68</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.31</v>
+        <v>6.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.45</v>
+        <v>8.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB15" t="n">
         <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.15</v>
+        <v>2.27</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AV15" t="n">
         <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.68</v>
+        <v>1.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>6.6</v>
+        <v>2.32</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN19" t="n">
         <v>1.85</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="U20" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="X20" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.86</v>
+        <v>4.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.74</v>
+        <v>2.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.2</v>
+        <v>4.12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="R21" t="n">
-        <v>4.28</v>
+        <v>15.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,130 +6120,130 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>3.59</v>
+        <v>4.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="T29" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="U29" t="n">
-        <v>4.12</v>
+        <v>5.05</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="X29" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
         <v>5.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AE29" t="n">
         <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC29" t="n">
         <v>1.95</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BF29" t="n">
         <v>1.22</v>
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q32" t="n">
         <v>4.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.69</v>
+        <v>3.6</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="T32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW32" t="n">
         <v>2.55</v>
       </c>
-      <c r="U32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE32" t="n">
+      <c r="AX32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
         <v>2.45</v>
       </c>
-      <c r="AG32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ32" t="n">
+      <c r="BF32" t="n">
         <v>1.46</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6989,52 +6989,52 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,137 +7101,137 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>6.95</v>
+        <v>3.36</v>
       </c>
       <c r="S34" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="V34" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="X34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT34" t="n">
         <v>2.48</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN34" t="n">
+      <c r="AU34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV34" t="n">
         <v>2.8</v>
       </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,67 +7302,67 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R35" t="n">
-        <v>3.36</v>
+        <v>4.19</v>
       </c>
       <c r="S35" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U35" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="V35" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="X35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK35" t="n">
         <v>1.43</v>
@@ -7371,61 +7371,61 @@
         <v>2.63</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AR35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
         <v>1.61</v>
       </c>
-      <c r="AS35" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,83 +7889,83 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8099,70 +8099,70 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.78</v>
+        <v>3.45</v>
       </c>
       <c r="R40" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,19 +8401,19 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>4.19</v>
+        <v>4.32</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11645,70 +11645,70 @@
         <v>3.1</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11750,19 +11750,19 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="R58" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY58" t="n">
         <v>0</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1395,34 +1395,34 @@
         <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="X5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="AA5" t="n">
         <v>1.04</v>
@@ -1431,16 +1431,16 @@
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
         <v>3.08</v>
@@ -1455,13 +1455,13 @@
         <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AN5" t="n">
         <v>1.35</v>
@@ -1509,13 +1509,13 @@
         <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
         <v>1.17</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>4.49</v>
+        <v>4.7</v>
       </c>
       <c r="S13" t="n">
         <v>2.15</v>
@@ -3004,7 +3004,7 @@
         <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC13" t="n">
         <v>1.27</v>
@@ -3037,10 +3037,10 @@
         <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>5.83</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
         <v>2.15</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
         <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31</v>
+        <v>6.46</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="X14" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z14" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AD14" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.15</v>
+        <v>2.27</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AR14" t="n">
         <v>2.05</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AV14" t="n">
         <v>2.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.68</v>
+        <v>1.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>5.68</v>
+        <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>6.52</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AV15" t="n">
         <v>2.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.5</v>
+        <v>1.63</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BD15" t="n">
         <v>3.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3607,7 +3607,7 @@
         <v>2.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AG16" t="n">
         <v>4.1</v>
@@ -3625,13 +3625,13 @@
         <v>2.06</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
@@ -3756,34 +3756,34 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.14</v>
+        <v>7.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>6.6</v>
+        <v>6.23</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
         <v>2.9</v>
       </c>
       <c r="X17" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
         <v>7</v>
@@ -3807,28 +3807,28 @@
         <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
         <v>3.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="T18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL18" t="n">
         <v>2.25</v>
       </c>
-      <c r="U18" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AM18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>4.56</v>
+        <v>4.95</v>
       </c>
       <c r="V20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.25</v>
       </c>
-      <c r="W20" t="n">
+      <c r="BC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD20" t="n">
         <v>3.6</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="BE20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,130 +5135,130 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>3.59</v>
+        <v>4.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>4.12</v>
+        <v>5.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
         <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AE24" t="n">
         <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
         <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BF24" t="n">
         <v>1.22</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="U29" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W29" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="X29" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="AM29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB29" t="n">
         <v>1.17</v>
       </c>
-      <c r="AN29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.95</v>
       </c>
-      <c r="BD29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6317,28 +6317,28 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="S30" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="T30" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W30" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="X30" t="n">
         <v>3.16</v>
@@ -6350,43 +6350,43 @@
         <v>7.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.98</v>
+        <v>4.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN30" t="n">
         <v>1.57</v>
@@ -6395,46 +6395,46 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="BD30" t="n">
         <v>3.22</v>
@@ -6443,7 +6443,7 @@
         <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,52 +6792,52 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,130 +6908,130 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,67 +7105,67 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R34" t="n">
-        <v>3.36</v>
+        <v>4.19</v>
       </c>
       <c r="S34" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="X34" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK34" t="n">
         <v>1.43</v>
@@ -7174,61 +7174,61 @@
         <v>2.63</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AR34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
         <v>1.61</v>
       </c>
-      <c r="AS34" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="T35" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="V35" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="W35" t="n">
-        <v>3.95</v>
+        <v>2.41</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AD35" t="n">
-        <v>6</v>
+        <v>2.46</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.41</v>
+        <v>2.41</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.06</v>
+        <v>4.9</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="AL35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC35" t="n">
         <v>2.63</v>
       </c>
-      <c r="AM35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.61</v>
-      </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="R38" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="S38" t="n">
         <v>1.84</v>
@@ -7923,7 +7923,7 @@
         <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA38" t="n">
         <v>1.12</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S39" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="T39" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
-        <v>4.18</v>
+        <v>3.6</v>
       </c>
       <c r="V39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BF39" t="n">
         <v>1.46</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>1.07</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="R40" t="n">
-        <v>5.6</v>
+        <v>2.63</v>
       </c>
       <c r="S40" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="V40" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="X40" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.74</v>
+        <v>2.99</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM40" t="n">
         <v>1.29</v>
       </c>
       <c r="AN40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA40" t="n">
         <v>2.06</v>
       </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="R41" t="n">
-        <v>2.67</v>
+        <v>5.6</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR46" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S48" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>6.23</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.07</v>
+        <v>4.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="X17" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
         <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
         <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
         <v>6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>4.28</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>6.23</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.95</v>
+        <v>2.07</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y20" t="n">
         <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
         <v>3.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN20" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.95</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
         <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
         <v>1.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.96</v>
+        <v>4.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.05</v>
+        <v>4.12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,70 +6720,70 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,130 +6908,130 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q33" t="n">
         <v>4.3</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z33" t="n">
         <v>4.2</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AA33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AM33" t="n">
         <v>1.19</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="AX33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY33" t="n">
         <v>1.58</v>
       </c>
-      <c r="AY33" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ33" t="n">
-        <v>2.95</v>
+        <v>1.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,130 +7105,130 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S35" t="n">
-        <v>2.79</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>4.18</v>
+        <v>2.16</v>
       </c>
       <c r="V35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>1.46</v>
       </c>
-      <c r="W35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,137 +7495,137 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.92</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.8</v>
+        <v>4.48</v>
       </c>
       <c r="R36" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W36" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="X36" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.16</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AD36" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.65</v>
+        <v>4.72</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,137 +7889,137 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.48</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="S38" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="T38" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="V38" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W38" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="X38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT38" t="n">
         <v>2.48</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN38" t="n">
+      <c r="AU38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV38" t="n">
         <v>2.8</v>
       </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.94</v>
+        <v>2.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="T47" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN47" t="n">
         <v>1.4</v>
       </c>
-      <c r="W47" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM47" t="n">
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX47" t="n">
+      <c r="BC47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE47" t="n">
         <v>1.53</v>
       </c>
-      <c r="AY47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF47" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R48" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U48" t="n">
-        <v>5.44</v>
+        <v>3.8</v>
       </c>
       <c r="V48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="Y48" t="n">
         <v>1.35</v>
       </c>
-      <c r="W48" t="n">
-        <v>3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z48" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AG48" t="n">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AI48" t="n">
-        <v>5.75</v>
+        <v>7.4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AN48" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.34</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AU48" t="n">
-        <v>4.45</v>
+        <v>3.97</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AY48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>1.46</v>
       </c>
-      <c r="AZ48" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BA48" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="S49" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="T49" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U49" t="n">
-        <v>6.2</v>
+        <v>5.44</v>
       </c>
       <c r="V49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W49" t="n">
+        <v>3</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>1.34</v>
       </c>
-      <c r="W49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AR49" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.87</v>
+        <v>4.45</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="BD49" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>2.13</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="S56" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="T56" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="U56" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="V56" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W56" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="X56" t="n">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z56" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AA56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB56" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC56" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AG56" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R57" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="T57" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="U57" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="V57" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W57" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="X57" t="n">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AF57" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE57" t="n">
         <v>1.69</v>
       </c>
-      <c r="AG57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF57" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11833,34 +11833,34 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R58" t="n">
         <v>3.8</v>
       </c>
       <c r="S58" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T58" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="U58" t="n">
-        <v>5.37</v>
+        <v>5.21</v>
       </c>
       <c r="V58" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W58" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="X58" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z58" t="n">
         <v>9.199999999999999</v>
@@ -11872,16 +11872,16 @@
         <v>1.11</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AE58" t="n">
         <v>2.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG58" t="n">
         <v>5.1</v>
@@ -11890,10 +11890,10 @@
         <v>1.12</v>
       </c>
       <c r="AI58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK58" t="n">
         <v>2.25</v>
@@ -11905,7 +11905,7 @@
         <v>1.34</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -11917,7 +11917,7 @@
         <v>1.87</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AS58" t="n">
         <v>3.2</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1392,34 +1392,34 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="T5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
         <v>3.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="X5" t="n">
         <v>2.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
         <v>7.1</v>
@@ -1428,7 +1428,7 @@
         <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
         <v>1.24</v>
@@ -1437,16 +1437,16 @@
         <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AF5" t="n">
         <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" t="n">
         <v>4.8</v>
@@ -1455,10 +1455,10 @@
         <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AM5" t="n">
         <v>1.27</v>
@@ -1470,49 +1470,49 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BB5" t="n">
         <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="BE5" t="n">
         <v>1.67</v>
@@ -1989,22 +1989,22 @@
         <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="S8" t="n">
         <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
         <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="X8" t="n">
         <v>2.5</v>
@@ -2025,7 +2025,7 @@
         <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AE8" t="n">
         <v>1.69</v>
@@ -2046,10 +2046,10 @@
         <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AM8" t="n">
         <v>1.3</v>
@@ -2061,55 +2061,55 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB8" t="n">
         <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3577,7 +3577,7 @@
         <v>4.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
         <v>2.44</v>
@@ -3607,7 +3607,7 @@
         <v>2.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AG16" t="n">
         <v>4.1</v>
@@ -3628,16 +3628,16 @@
         <v>1.73</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.61</v>
@@ -3646,31 +3646,31 @@
         <v>2.33</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AW16" t="n">
         <v>1.72</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BB16" t="n">
         <v>1.29</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>6.23</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>4.95</v>
+        <v>2.07</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="Y17" t="n">
         <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
         <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" t="n">
         <v>6</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4159,13 +4159,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="U19" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
@@ -4174,52 +4174,52 @@
         <v>3.08</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.05</v>
+        <v>6.2</v>
       </c>
       <c r="AA19" t="n">
         <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AN19" t="n">
         <v>2</v>
@@ -4228,55 +4228,55 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.04</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
-        <v>6.23</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X20" t="n">
         <v>2.2</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.96</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
         <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.85</v>
+        <v>4.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>4.12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AM20" t="n">
         <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.11</v>
+        <v>2.15</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.25</v>
       </c>
-      <c r="W21" t="n">
+      <c r="BC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD21" t="n">
         <v>3.6</v>
       </c>
-      <c r="X21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="BE21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="U24" t="n">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W24" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.17</v>
       </c>
-      <c r="AN24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE24" t="n">
         <v>1.95</v>
       </c>
-      <c r="BD24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>3.5</v>
+        <v>5.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="X26" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB26" t="n">
         <v>1.01</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.18</v>
       </c>
-      <c r="AD26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="S32" t="n">
-        <v>2.79</v>
+        <v>2.12</v>
       </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="U32" t="n">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="V32" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>2.41</v>
+        <v>3.95</v>
       </c>
       <c r="X32" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.46</v>
+        <v>6</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.41</v>
+        <v>1.41</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.9</v>
+        <v>2.06</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.63</v>
+        <v>1.61</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,137 +6904,137 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.3</v>
+        <v>4.48</v>
       </c>
       <c r="R33" t="n">
-        <v>4.19</v>
+        <v>6.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U33" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="V33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM33" t="n">
         <v>1.2</v>
       </c>
-      <c r="W33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z33" t="n">
+      <c r="AN33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD33" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
       <c r="BE33" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,130 +7105,130 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q35" t="n">
         <v>4.3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>4.2</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.69</v>
+        <v>3.6</v>
       </c>
       <c r="S35" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="T35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW35" t="n">
         <v>2.55</v>
       </c>
-      <c r="U35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE35" t="n">
+      <c r="AX35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
         <v>1.47</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
         <v>2.45</v>
       </c>
-      <c r="AG35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ35" t="n">
+      <c r="BF35" t="n">
         <v>1.46</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,137 +7495,137 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.36</v>
+        <v>4.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>6.5</v>
+        <v>1.69</v>
       </c>
       <c r="S36" t="n">
-        <v>1.84</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
         <v>2.55</v>
       </c>
       <c r="U36" t="n">
-        <v>6.5</v>
+        <v>2.16</v>
       </c>
       <c r="V36" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W36" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="X36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV36" t="n">
         <v>2.48</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X38" t="n">
         <v>3.5</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="Y38" t="n">
         <v>1.23</v>
       </c>
-      <c r="W38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Z38" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AD38" t="n">
-        <v>5.3</v>
+        <v>2.46</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.48</v>
+        <v>2.41</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="AL38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC38" t="n">
         <v>2.63</v>
       </c>
-      <c r="AM38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.02</v>
+        <v>1.39</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8171,52 +8171,52 @@
         <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR46" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9747,7 +9747,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R56" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="S56" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="T56" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="U56" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="V56" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W56" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="X56" t="n">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AF56" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE56" t="n">
         <v>1.69</v>
       </c>
-      <c r="AG56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF56" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.59</v>
+        <v>2.13</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="S57" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="T57" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="U57" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="V57" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W57" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="X57" t="n">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB57" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB57" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC57" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BA57" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11833,19 +11833,19 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q58" t="n">
         <v>2.7</v>
       </c>
       <c r="R58" t="n">
-        <v>3.8</v>
+        <v>4.96</v>
       </c>
       <c r="S58" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="T58" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="U58" t="n">
         <v>5.21</v>
@@ -11902,7 +11902,7 @@
         <v>1.57</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AN58" t="n">
         <v>1.67</v>
@@ -11911,37 +11911,37 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.87</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AS58" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AU58" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="AV58" t="n">
         <v>1.81</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="BA58" t="n">
         <v>2.5</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3168,109 +3168,109 @@
         <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="U14" t="n">
-        <v>6.46</v>
+        <v>6.51</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="X14" t="n">
         <v>3.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AE14" t="n">
         <v>2.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG14" t="n">
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
         <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AM14" t="n">
         <v>1.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.45</v>
+        <v>4.18</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.38</v>
@@ -3279,19 +3279,19 @@
         <v>3.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
         <v>4.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
         <v>1.94</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.04</v>
+        <v>1.17</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>15.5</v>
       </c>
       <c r="S17" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="T19" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="X19" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.9</v>
+        <v>4.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.74</v>
+        <v>2.41</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.2</v>
+        <v>4.12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>7.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>6.23</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.5</v>
+        <v>2.07</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
         <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.68</v>
+        <v>3.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.12</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.59</v>
+        <v>2.01</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AM20" t="n">
         <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
         <v>1.36</v>
@@ -4583,10 +4583,10 @@
         <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AE21" t="n">
         <v>1.86</v>
@@ -4610,10 +4610,10 @@
         <v>1.75</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
         <v>1.95</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="U24" t="n">
-        <v>3.5</v>
+        <v>4.13</v>
       </c>
       <c r="V24" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="T27" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
-        <v>4.13</v>
+        <v>5.05</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="X27" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
         <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AE27" t="n">
         <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" t="n">
         <v>5.15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
         <v>4.3</v>
       </c>
       <c r="R32" t="n">
-        <v>4.19</v>
+        <v>3.6</v>
       </c>
       <c r="S32" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W32" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="X32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX32" t="n">
         <v>2</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV32" t="n">
+      <c r="AY32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA32" t="n">
         <v>3.15</v>
       </c>
-      <c r="AW32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,25 +7105,25 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>3.5</v>
+        <v>1.69</v>
       </c>
       <c r="S34" t="n">
-        <v>2.43</v>
+        <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
-        <v>3.65</v>
+        <v>2.16</v>
       </c>
       <c r="V34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
         <v>3.7</v>
@@ -7132,7 +7132,7 @@
         <v>2.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z34" t="n">
         <v>4.5</v>
@@ -7150,85 +7150,85 @@
         <v>5.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX34" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AY34" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.71</v>
+        <v>2.95</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" t="n">
         <v>4.3</v>
       </c>
       <c r="R35" t="n">
-        <v>3.6</v>
+        <v>4.19</v>
       </c>
       <c r="S35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT35" t="n">
         <v>2.2</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BB35" t="n">
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,25 +7499,25 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.69</v>
+        <v>3.5</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>2.43</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>2.16</v>
+        <v>3.65</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
         <v>3.7</v>
@@ -7526,7 +7526,7 @@
         <v>2.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
         <v>4.5</v>
@@ -7544,85 +7544,85 @@
         <v>5.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AJ36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM36" t="n">
         <v>1.22</v>
       </c>
-      <c r="AK36" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AN36" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY36" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ36" t="n">
-        <v>2.95</v>
+        <v>1.71</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7902,19 +7902,19 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="T38" t="n">
         <v>1.95</v>
       </c>
       <c r="U38" t="n">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="V38" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W38" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="X38" t="n">
         <v>3.5</v>
@@ -7929,19 +7929,19 @@
         <v>1.01</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG38" t="n">
         <v>4.9</v>
@@ -8007,13 +8007,13 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BC38" t="n">
         <v>2.63</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BE38" t="n">
         <v>1.39</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R40" t="n">
-        <v>2.63</v>
+        <v>5.6</v>
       </c>
       <c r="S40" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="U40" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="X40" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI40" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AM40" t="n">
         <v>1.29</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE40" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF40" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="R41" t="n">
-        <v>5.6</v>
+        <v>2.63</v>
       </c>
       <c r="S41" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="V41" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="X41" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.74</v>
+        <v>2.99</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI41" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM41" t="n">
         <v>1.29</v>
       </c>
       <c r="AN41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA41" t="n">
         <v>2.06</v>
       </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9353,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR45" t="n">
         <v>0</v>
@@ -9368,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI49" t="n">
         <v>4.8</v>
       </c>
-      <c r="S49" t="n">
+      <c r="AJ49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN49" t="n">
         <v>2.3</v>
       </c>
-      <c r="T49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U49" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM49" t="n">
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
         <v>1.2</v>
       </c>
-      <c r="AN49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AQ49" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AU49" t="n">
-        <v>4.45</v>
+        <v>3.87</v>
       </c>
       <c r="AV49" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="BD49" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R53" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="S53" t="n">
         <v>3.41</v>
@@ -10881,7 +10881,7 @@
         <v>8.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB53" t="n">
         <v>1.02</v>
@@ -10893,7 +10893,7 @@
         <v>2.74</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AF53" t="n">
         <v>1.64</v>
@@ -10905,19 +10905,19 @@
         <v>1.17</v>
       </c>
       <c r="AI53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ53" t="n">
         <v>1.02</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN53" t="n">
         <v>1.44</v>
@@ -10926,55 +10926,55 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AZ53" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC53" t="n">
         <v>2.4</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11242,19 +11242,19 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="S55" t="n">
         <v>3.4</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U55" t="n">
         <v>3</v>
@@ -11263,7 +11263,7 @@
         <v>1.4</v>
       </c>
       <c r="W55" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X55" t="n">
         <v>2.94</v>
@@ -11278,19 +11278,19 @@
         <v>1.07</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC55" t="n">
         <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG55" t="n">
         <v>3.54</v>
@@ -11305,16 +11305,16 @@
         <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL55" t="n">
         <v>1.91</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11350,25 +11350,25 @@
         <v>1.33</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BA55" t="n">
         <v>2.2</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>3.31</v>
       </c>
       <c r="S56" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="T56" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="U56" t="n">
-        <v>5.2</v>
+        <v>4.26</v>
       </c>
       <c r="V56" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W56" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="X56" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z56" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AF56" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL56" t="n">
         <v>1.87</v>
       </c>
-      <c r="AG56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AM56" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.35</v>
+        <v>1.61</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.13</v>
+        <v>1.52</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R57" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="S57" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="T57" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="U57" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="V57" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W57" t="n">
-        <v>2.53</v>
+        <v>3.03</v>
       </c>
       <c r="X57" t="n">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z57" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BE57" t="n">
         <v>1.69</v>
       </c>
-      <c r="AG57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF57" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1392,34 +1392,34 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="S5" t="n">
         <v>3.42</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="n">
         <v>3.04</v>
       </c>
       <c r="V5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.37</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
         <v>7.1</v>
@@ -1440,13 +1440,13 @@
         <v>1.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
         <v>4.8</v>
@@ -1506,19 +1506,19 @@
         <v>1.57</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
         <v>2.07</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="BE5" t="n">
         <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
         <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="T13" t="n">
         <v>2.2</v>
@@ -2998,13 +2998,13 @@
         <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
         <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
         <v>1.27</v>
@@ -3016,7 +3016,7 @@
         <v>1.92</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
         <v>3.17</v>
@@ -3037,64 +3037,64 @@
         <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AU13" t="n">
         <v>3.42</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3371,13 +3371,13 @@
         <v>1.95</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>4.79</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
         <v>1.4</v>
@@ -3401,10 +3401,10 @@
         <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AE15" t="n">
         <v>2.05</v>
@@ -3416,25 +3416,25 @@
         <v>3.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" t="n">
         <v>6.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
         <v>1.8</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AM15" t="n">
         <v>1.24</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4162,16 +4162,16 @@
         <v>2.12</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X19" t="n">
         <v>2.2</v>
@@ -4180,7 +4180,7 @@
         <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA19" t="n">
         <v>1.14</v>
@@ -4204,13 +4204,13 @@
         <v>2.41</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" t="n">
         <v>4.12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK19" t="n">
         <v>1.59</v>
@@ -4219,10 +4219,10 @@
         <v>2.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4350,31 +4350,31 @@
         <v>7.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
         <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>6.23</v>
+        <v>6.03</v>
       </c>
       <c r="T20" t="n">
         <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
         <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
         <v>7</v>
@@ -4383,7 +4383,7 @@
         <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
         <v>1.17</v>
@@ -4398,28 +4398,28 @@
         <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,13 +4461,13 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
         <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BE20" t="n">
         <v>1.62</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4553,124 +4553,124 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>4.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AF21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV21" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL21" t="n">
+      <c r="AW21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>1.89</v>
       </c>
-      <c r="AM21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="U24" t="n">
-        <v>4.13</v>
+        <v>3.77</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AM24" t="n">
         <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.16</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6317,22 +6317,22 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="S30" t="n">
         <v>2.85</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U30" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="V30" t="n">
         <v>1.45</v>
@@ -6350,10 +6350,10 @@
         <v>7.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC30" t="n">
         <v>1.4</v>
@@ -6371,22 +6371,22 @@
         <v>4.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI30" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
         <v>1.57</v>
@@ -6395,46 +6395,46 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.34</v>
+        <v>2.99</v>
       </c>
       <c r="AV30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC30" t="n">
         <v>2.39</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.4</v>
       </c>
       <c r="BD30" t="n">
         <v>3.22</v>
@@ -6443,7 +6443,7 @@
         <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6517,19 +6517,19 @@
         <v>1.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="S31" t="n">
         <v>2.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>4.34</v>
+        <v>3.65</v>
       </c>
       <c r="V31" t="n">
         <v>1.36</v>
@@ -6571,61 +6571,61 @@
         <v>1.33</v>
       </c>
       <c r="AI31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL31" t="n">
         <v>2</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="BB31" t="n">
         <v>1.25</v>
@@ -6634,13 +6634,13 @@
         <v>2.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="BE31" t="n">
         <v>1.67</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,137 +6707,137 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR32" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="AS32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.15</v>
       </c>
-      <c r="W32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="BC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.46</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,83 +6904,83 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.84</v>
+        <v>2.77</v>
       </c>
       <c r="T33" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="U33" t="n">
-        <v>6.5</v>
+        <v>4.24</v>
       </c>
       <c r="V33" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="W33" t="n">
-        <v>3.3</v>
+        <v>2.39</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>2.43</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.64</v>
+        <v>4.9</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.72</v>
+        <v>10</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.9</v>
+        <v>1.39</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,130 +7105,130 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S38" t="n">
-        <v>2.77</v>
+        <v>2.43</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>4.24</v>
+        <v>3.65</v>
       </c>
       <c r="V38" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="W38" t="n">
-        <v>2.39</v>
+        <v>3.7</v>
       </c>
       <c r="X38" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z38" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK38" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8171,52 +8171,52 @@
         <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="R40" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="T40" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U40" t="n">
-        <v>6</v>
+        <v>6.31</v>
       </c>
       <c r="V40" t="n">
         <v>1.53</v>
@@ -8311,7 +8311,7 @@
         <v>2.24</v>
       </c>
       <c r="X40" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="Y40" t="n">
         <v>1.28</v>
@@ -8332,34 +8332,34 @@
         <v>2.74</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK40" t="n">
         <v>2.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,13 +8401,13 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC40" t="n">
         <v>2.24</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="BE40" t="n">
         <v>1.56</v>
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S41" t="n">
         <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="U41" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V41" t="n">
         <v>1.37</v>
@@ -8508,28 +8508,28 @@
         <v>2.8</v>
       </c>
       <c r="X41" t="n">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AF41" t="n">
         <v>1.7</v>
@@ -8553,7 +8553,7 @@
         <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AN41" t="n">
         <v>1.46</v>
@@ -8562,55 +8562,55 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AX41" t="n">
         <v>1.37</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AZ41" t="n">
         <v>1.88</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="BB41" t="n">
         <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BD41" t="n">
         <v>3.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9353,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
         <v>0</v>
@@ -9368,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9866,22 +9866,22 @@
         <v>2.26</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="R48" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="T48" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="U48" t="n">
         <v>3.8</v>
       </c>
       <c r="V48" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W48" t="n">
         <v>2.65</v>
@@ -9893,13 +9893,13 @@
         <v>1.35</v>
       </c>
       <c r="Z48" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AA48" t="n">
         <v>1.02</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC48" t="n">
         <v>1.4</v>
@@ -9911,7 +9911,7 @@
         <v>2.21</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG48" t="n">
         <v>4.2</v>
@@ -9932,10 +9932,10 @@
         <v>1.79</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9947,49 +9947,49 @@
         <v>1.34</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.97</v>
+        <v>3.82</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BA48" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC48" t="n">
         <v>2.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BE48" t="n">
         <v>1.52</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10069,13 +10069,13 @@
         <v>5.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="T49" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="U49" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="V49" t="n">
         <v>1.34</v>
@@ -10084,10 +10084,10 @@
         <v>3.25</v>
       </c>
       <c r="X49" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
         <v>6.05</v>
@@ -10102,22 +10102,22 @@
         <v>1.19</v>
       </c>
       <c r="AD49" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AG49" t="n">
         <v>2.83</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AJ49" t="n">
         <v>1.15</v>
@@ -10132,13 +10132,13 @@
         <v>1.16</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.38</v>
@@ -10153,7 +10153,7 @@
         <v>2.55</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="AV49" t="n">
         <v>2.82</v>
@@ -10180,7 +10180,7 @@
         <v>1.95</v>
       </c>
       <c r="BD49" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="BE49" t="n">
         <v>1.7</v>
@@ -10257,31 +10257,31 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="S50" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="T50" t="n">
         <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>5.44</v>
+        <v>5.26</v>
       </c>
       <c r="V50" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W50" t="n">
         <v>3</v>
       </c>
       <c r="X50" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Y50" t="n">
         <v>1.43</v>
@@ -10293,49 +10293,49 @@
         <v>1.07</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AE50" t="n">
         <v>1.97</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AI50" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL50" t="n">
         <v>1.96</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AN50" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.34</v>
@@ -10344,31 +10344,31 @@
         <v>1.81</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AU50" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="BB50" t="n">
         <v>1.25</v>
@@ -10377,10 +10377,10 @@
         <v>2.15</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="BF50" t="n">
         <v>1.18</v>
@@ -10654,16 +10654,16 @@
         <v>1.83</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R52" t="n">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="S52" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="T52" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U52" t="n">
         <v>4.2</v>
@@ -10672,7 +10672,7 @@
         <v>1.37</v>
       </c>
       <c r="W52" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="X52" t="n">
         <v>2.73</v>
@@ -10693,7 +10693,7 @@
         <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AE52" t="n">
         <v>1.91</v>
@@ -10717,10 +10717,10 @@
         <v>1.73</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN52" t="n">
         <v>1.84</v>
@@ -10729,55 +10729,55 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AS52" t="n">
         <v>1.9</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.44</v>
+        <v>2.83</v>
       </c>
       <c r="AU52" t="n">
-        <v>4.45</v>
+        <v>3.76</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.94</v>
+        <v>2.53</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.06</v>
+        <v>2.74</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BC52" t="n">
         <v>2.09</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="BE52" t="n">
         <v>1.68</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -11833,16 +11833,16 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="R58" t="n">
-        <v>4.96</v>
+        <v>3.8</v>
       </c>
       <c r="S58" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="T58" t="n">
         <v>1.72</v>
@@ -11881,7 +11881,7 @@
         <v>2.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG58" t="n">
         <v>5.1</v>
@@ -11902,10 +11902,10 @@
         <v>1.57</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -11944,7 +11944,7 @@
         <v>1.31</v>
       </c>
       <c r="BA58" t="n">
-        <v>2.5</v>
+        <v>5.09</v>
       </c>
       <c r="BB58" t="n">
         <v>1.36</v>
@@ -11953,7 +11953,7 @@
         <v>2.56</v>
       </c>
       <c r="BD58" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BE58" t="n">
         <v>1.42</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>4.49</v>
+        <v>5.25</v>
       </c>
       <c r="S13" t="n">
         <v>2.13</v>
@@ -3046,40 +3046,40 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="BB13" t="n">
         <v>1.19</v>
@@ -3565,16 +3565,16 @@
         <v>2.98</v>
       </c>
       <c r="R16" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U16" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="V16" t="n">
         <v>1.48</v>
@@ -3583,7 +3583,7 @@
         <v>2.44</v>
       </c>
       <c r="X16" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
         <v>1.28</v>
@@ -3598,40 +3598,40 @@
         <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.02</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,16 +3673,16 @@
         <v>4.05</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF16" t="n">
         <v>1.08</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.17</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4165,7 +4165,7 @@
         <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.23</v>
@@ -4201,7 +4201,7 @@
         <v>2.28</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="AH19" t="n">
         <v>1.53</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,58 +6120,58 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="U29" t="n">
-        <v>5.05</v>
+        <v>4.13</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="X29" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
         <v>5.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AE29" t="n">
         <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AH29" t="n">
         <v>1.34</v>
@@ -6183,70 +6183,70 @@
         <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.18</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
         <v>3.1</v>
@@ -6395,22 +6395,22 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.59</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AV30" t="n">
         <v>2.18</v>
@@ -6425,10 +6425,10 @@
         <v>1.23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="BB30" t="n">
         <v>1.29</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,137 +6707,137 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.4</v>
+        <v>4.13</v>
       </c>
       <c r="R32" t="n">
-        <v>6.98</v>
+        <v>3.31</v>
       </c>
       <c r="S32" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="T32" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>6.5</v>
+        <v>3.65</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AI32" t="n">
-        <v>4.72</v>
+        <v>3.65</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.82</v>
+        <v>1.43</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AS32" t="n">
         <v>1.96</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.36</v>
+        <v>3.85</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6917,70 +6917,70 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7114,70 +7114,70 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="R35" t="n">
-        <v>4.19</v>
+        <v>3.3</v>
       </c>
       <c r="S35" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="V35" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="X35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX35" t="n">
         <v>2</v>
       </c>
-      <c r="Y35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV35" t="n">
+      <c r="AY35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA35" t="n">
         <v>3.15</v>
       </c>
-      <c r="AW35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BB35" t="n">
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,130 +7499,130 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,137 +7692,137 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.69</v>
+        <v>6.98</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>1.84</v>
       </c>
       <c r="T37" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U37" t="n">
-        <v>2.16</v>
+        <v>6.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W37" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="X37" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC37" t="n">
         <v>1.16</v>
       </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD37" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AQ37" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AR37" t="n">
         <v>1.75</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.4</v>
+        <v>4.36</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.95</v>
+        <v>1.13</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,25 +7893,25 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.95</v>
+        <v>3.99</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="R38" t="n">
-        <v>3.5</v>
+        <v>1.72</v>
       </c>
       <c r="S38" t="n">
-        <v>2.43</v>
+        <v>4.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U38" t="n">
-        <v>3.65</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
         <v>3.7</v>
@@ -7920,7 +7920,7 @@
         <v>2.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z38" t="n">
         <v>4.5</v>
@@ -7938,85 +7938,85 @@
         <v>5.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX38" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AY38" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.71</v>
+        <v>2.95</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="BB38" t="n">
         <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8171,52 +8171,52 @@
         <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="S40" t="n">
         <v>2.27</v>
@@ -8335,7 +8335,7 @@
         <v>2.14</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG40" t="n">
         <v>3.58</v>
@@ -8401,13 +8401,13 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
         <v>2.24</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
         <v>1.56</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
         <v>2.9</v>
@@ -8496,7 +8496,7 @@
         <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="U41" t="n">
         <v>3.2</v>
@@ -8514,7 +8514,7 @@
         <v>1.32</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AA41" t="n">
         <v>1.02</v>
@@ -8523,13 +8523,13 @@
         <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AF41" t="n">
         <v>1.7</v>
@@ -8553,10 +8553,10 @@
         <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8571,7 +8571,7 @@
         <v>2.38</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AT41" t="n">
         <v>3.58</v>
@@ -8580,7 +8580,7 @@
         <v>2.97</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AW41" t="n">
         <v>1.72</v>
@@ -8595,19 +8595,19 @@
         <v>1.88</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BB41" t="n">
         <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="BD41" t="n">
         <v>3.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BF41" t="n">
         <v>1.12</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.26</v>
+        <v>1.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W48" t="n">
         <v>3</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W48" t="n">
-        <v>2.65</v>
-      </c>
       <c r="X48" t="n">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z48" t="n">
         <v>7</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AG48" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AI48" t="n">
-        <v>7.4</v>
+        <v>6.05</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.34</v>
       </c>
       <c r="AR48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE48" t="n">
         <v>1.71</v>
       </c>
-      <c r="AS48" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>1.52</v>
-      </c>
       <c r="BF48" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>6.21</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U50" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR50" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R50" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U50" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="V50" t="n">
+      <c r="AS50" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>1.33</v>
       </c>
-      <c r="W50" t="n">
-        <v>3</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BA50" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10702,7 +10702,7 @@
         <v>1.83</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AH52" t="n">
         <v>1.3</v>
@@ -10732,25 +10732,25 @@
         <v>1.19</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AS52" t="n">
         <v>1.9</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="AV52" t="n">
         <v>2.53</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AX52" t="n">
         <v>1.6</v>
@@ -10759,10 +10759,10 @@
         <v>1.32</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BA52" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BB52" t="n">
         <v>1.21</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="Q58" t="n">
         <v>2.85</v>
@@ -11842,7 +11842,7 @@
         <v>3.8</v>
       </c>
       <c r="S58" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="T58" t="n">
         <v>1.72</v>
@@ -11881,7 +11881,7 @@
         <v>2.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG58" t="n">
         <v>5.1</v>
@@ -11899,7 +11899,7 @@
         <v>2.25</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AM58" t="n">
         <v>1.4</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="S16" t="n">
         <v>2.68</v>
@@ -3637,40 +3637,40 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AZ16" t="n">
         <v>1.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="BB16" t="n">
         <v>1.28</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,124 +3765,124 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>4.95</v>
+        <v>4.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AW17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>1.89</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>3.7</v>
+        <v>2.73</v>
       </c>
       <c r="X19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.68</v>
+        <v>3.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.12</v>
+        <v>6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>3.78</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>7.04</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W20" t="n">
         <v>3.7</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
         <v>2.2</v>
       </c>
-      <c r="U20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.01</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
         <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.85</v>
+        <v>4.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.28</v>
+        <v>2.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.15</v>
+        <v>4.12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE32" t="n">
         <v>2.43</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF32" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="AL32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC32" t="n">
         <v>2.63</v>
       </c>
-      <c r="AM32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.02</v>
+        <v>1.39</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,137 +6904,137 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7114,70 +7114,70 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,67 +7499,67 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.52</v>
+        <v>4.13</v>
       </c>
       <c r="R36" t="n">
-        <v>4.58</v>
+        <v>3.31</v>
       </c>
       <c r="S36" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="T36" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AD36" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK36" t="n">
         <v>1.43</v>
@@ -7568,61 +7568,61 @@
         <v>2.63</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN36" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,137 +7692,137 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="Q37" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU37" t="n">
         <v>4.4</v>
       </c>
-      <c r="R37" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="AV37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA37" t="n">
         <v>3.3</v>
       </c>
-      <c r="X37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE37" t="n">
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
         <v>1.61</v>
       </c>
-      <c r="AF37" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BD37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>5.6</v>
+        <v>2.56</v>
       </c>
       <c r="S40" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="U40" t="n">
-        <v>6.31</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="X40" t="n">
-        <v>3.11</v>
+        <v>3.37</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA40" t="n">
         <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT40" t="n">
         <v>3.58</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AU40" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY40" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI40" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.56</v>
+        <v>5.6</v>
       </c>
       <c r="S41" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="T41" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="U41" t="n">
-        <v>3.2</v>
+        <v>6.31</v>
       </c>
       <c r="V41" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W41" t="n">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="X41" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
         <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI41" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S44" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="U44" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W44" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="X44" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
         <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="AH44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN44" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI44" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.14</v>
+        <v>2.36</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R48" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U48" t="n">
-        <v>5.32</v>
+        <v>6.21</v>
       </c>
       <c r="V48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>1.33</v>
       </c>
-      <c r="W48" t="n">
-        <v>3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BA48" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>6.21</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="S51" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="T51" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>3.8</v>
+        <v>5.32</v>
       </c>
       <c r="V51" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="X51" t="n">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z51" t="n">
         <v>7</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AE51" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AG51" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>7.4</v>
+        <v>6.05</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.34</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.83</v>
+        <v>2.36</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.72</v>
+        <v>4.25</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.62</v>
+        <v>4.75</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -11242,19 +11242,19 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="S55" t="n">
         <v>3.4</v>
       </c>
       <c r="T55" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="U55" t="n">
         <v>3</v>
@@ -11263,10 +11263,10 @@
         <v>1.4</v>
       </c>
       <c r="W55" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="X55" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="Y55" t="n">
         <v>1.36</v>
@@ -11314,7 +11314,7 @@
         <v>1.34</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="S56" t="n">
         <v>2.72</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -810,70 +810,70 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>7.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.12</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>3.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
         <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.68</v>
+        <v>3.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.34</v>
+        <v>3.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.12</v>
+        <v>6.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>7.04</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>6.03</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>4.95</v>
       </c>
       <c r="V21" t="n">
         <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="X21" t="n">
-        <v>3.01</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.85</v>
+        <v>3.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AL21" t="n">
         <v>1.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,16 +4658,16 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BF21" t="n">
         <v>1.15</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5335,7 +5335,7 @@
         <v>1.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
         <v>4.33</v>
@@ -5362,7 +5362,7 @@
         <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
         <v>1.1</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,70 +6720,70 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,137 +6904,137 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.36</v>
+        <v>3.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.4</v>
+        <v>4.01</v>
       </c>
       <c r="R33" t="n">
-        <v>6.98</v>
+        <v>1.72</v>
       </c>
       <c r="S33" t="n">
-        <v>1.84</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF33" t="n">
         <v>2.45</v>
       </c>
-      <c r="U33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AG33" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.72</v>
+        <v>3.95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.8</v>
+        <v>1.17</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AR33" t="n">
         <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>4.36</v>
+        <v>3.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.13</v>
+        <v>2.95</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,52 +7186,52 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="T35" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="U35" t="n">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="W35" t="n">
-        <v>4.6</v>
+        <v>2.39</v>
       </c>
       <c r="X35" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.27</v>
+        <v>2.43</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.72</v>
+        <v>4.9</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.3</v>
+        <v>2.08</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,52 +7383,52 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.47</v>
+        <v>2.63</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,137 +7495,137 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
       <c r="R36" t="n">
-        <v>3.31</v>
+        <v>6.98</v>
       </c>
       <c r="S36" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U36" t="n">
-        <v>3.65</v>
+        <v>6.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W36" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="X36" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.16</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN36" t="n">
+      <c r="AQ36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR36" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.61</v>
       </c>
       <c r="AS36" t="n">
         <v>1.96</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.85</v>
+        <v>4.36</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,25 +7893,25 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.99</v>
+        <v>1.87</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.01</v>
+        <v>4.13</v>
       </c>
       <c r="R38" t="n">
-        <v>1.72</v>
+        <v>3.31</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>2.43</v>
       </c>
       <c r="T38" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>2.16</v>
+        <v>3.65</v>
       </c>
       <c r="V38" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W38" t="n">
         <v>3.7</v>
@@ -7920,7 +7920,7 @@
         <v>2.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
         <v>4.5</v>
@@ -7938,85 +7938,85 @@
         <v>5.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AJ38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM38" t="n">
         <v>1.22</v>
       </c>
-      <c r="AK38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AN38" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>2.95</v>
+        <v>1.71</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="BB38" t="n">
         <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.56</v>
+        <v>5.6</v>
       </c>
       <c r="S40" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="T40" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="U40" t="n">
-        <v>3.2</v>
+        <v>6.31</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="X40" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
         <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI40" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>5.6</v>
+        <v>2.56</v>
       </c>
       <c r="S41" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="U41" t="n">
-        <v>6.31</v>
+        <v>3.2</v>
       </c>
       <c r="V41" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="X41" t="n">
-        <v>3.11</v>
+        <v>3.37</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA41" t="n">
         <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT41" t="n">
         <v>3.58</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AU41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY41" t="n">
         <v>1.21</v>
       </c>
-      <c r="AI41" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="R43" t="n">
-        <v>2.1</v>
+        <v>4.98</v>
       </c>
       <c r="S43" t="n">
-        <v>3.58</v>
+        <v>2.18</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="U43" t="n">
-        <v>3.24</v>
+        <v>5.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W43" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="X43" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>6.35</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.99</v>
+        <v>3.54</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.85</v>
+        <v>2.89</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>6.35</v>
+        <v>5.45</v>
       </c>
       <c r="AJ43" t="n">
         <v>1.08</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="R44" t="n">
         <v>1.97</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>4.32</v>
       </c>
       <c r="T44" t="n">
         <v>2.13</v>
       </c>
       <c r="U44" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V44" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="X44" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z44" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD44" t="n">
+      <c r="AK44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU44" t="n">
         <v>3.44</v>
       </c>
-      <c r="AE44" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AJ44" t="n">
+      <c r="AV44" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF44" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="R48" t="n">
-        <v>5.5</v>
+        <v>3.82</v>
       </c>
       <c r="S48" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="T48" t="n">
         <v>2.21</v>
       </c>
       <c r="U48" t="n">
-        <v>6.21</v>
+        <v>4.42</v>
       </c>
       <c r="V48" t="n">
         <v>1.34</v>
       </c>
       <c r="W48" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="X48" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.05</v>
+        <v>5.9</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="AE48" t="n">
         <v>1.74</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI48" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="AJ48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK48" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AQ48" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AV48" t="n">
         <v>2.82</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="R49" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.85</v>
+        <v>2.08</v>
       </c>
       <c r="T49" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="U49" t="n">
-        <v>3.8</v>
+        <v>6.21</v>
       </c>
       <c r="V49" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="W49" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="X49" t="n">
-        <v>3.31</v>
+        <v>2.54</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
-        <v>7</v>
+        <v>6.05</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AB49" t="n">
         <v>1.04</v>
       </c>
       <c r="AC49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD49" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BA49" t="n">
         <v>4.2</v>
       </c>
-      <c r="AH49" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>3.62</v>
-      </c>
       <c r="BB49" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="BD49" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10881,7 +10881,7 @@
         <v>8.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB53" t="n">
         <v>1.02</v>
@@ -10896,7 +10896,7 @@
         <v>2.21</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG53" t="n">
         <v>4.16</v>
@@ -10911,10 +10911,10 @@
         <v>1.02</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AM53" t="n">
         <v>1.32</v>
@@ -10932,22 +10932,22 @@
         <v>1.6</v>
       </c>
       <c r="AR53" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AT53" t="n">
         <v>3.6</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AX53" t="n">
         <v>1.39</v>
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S55" t="n">
         <v>3.4</v>
@@ -11269,7 +11269,7 @@
         <v>2.99</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z55" t="n">
         <v>8</v>
@@ -11323,7 +11323,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AR55" t="n">
         <v>1.85</v>
@@ -11338,7 +11338,7 @@
         <v>3.78</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW55" t="n">
         <v>2.01</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="S56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R56" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.72</v>
-      </c>
       <c r="T56" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="U56" t="n">
-        <v>4.26</v>
+        <v>5.55</v>
       </c>
       <c r="V56" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W56" t="n">
-        <v>2.53</v>
+        <v>2.84</v>
       </c>
       <c r="X56" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z56" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX56" t="n">
         <v>1.69</v>
       </c>
-      <c r="AG56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.52</v>
+        <v>1.97</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>4.95</v>
+        <v>3.31</v>
       </c>
       <c r="S57" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="T57" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="U57" t="n">
-        <v>5.2</v>
+        <v>4.26</v>
       </c>
       <c r="V57" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W57" t="n">
-        <v>3.03</v>
+        <v>2.57</v>
       </c>
       <c r="X57" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>5.55</v>
+        <v>6.75</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA57" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="R58" t="n">
-        <v>3.8</v>
+        <v>4.96</v>
       </c>
       <c r="S58" t="n">
         <v>2.8</v>
@@ -11848,7 +11848,7 @@
         <v>1.72</v>
       </c>
       <c r="U58" t="n">
-        <v>5.21</v>
+        <v>4.8</v>
       </c>
       <c r="V58" t="n">
         <v>1.68</v>
@@ -11857,10 +11857,10 @@
         <v>2.05</v>
       </c>
       <c r="X58" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z58" t="n">
         <v>9.199999999999999</v>
@@ -11881,7 +11881,7 @@
         <v>2.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG58" t="n">
         <v>5.1</v>
@@ -11902,7 +11902,7 @@
         <v>1.59</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AN58" t="n">
         <v>1.68</v>

--- a/jogos_2026-03-16.xlsx
+++ b/jogos_2026-03-16.xlsx
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
         <v>3.42</v>
@@ -1419,7 +1419,7 @@
         <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
         <v>7.1</v>
@@ -1455,13 +1455,13 @@
         <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL5" t="n">
         <v>2.04</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
         <v>1.35</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.55</v>
+        <v>7.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.84</v>
+        <v>2.88</v>
       </c>
       <c r="AE8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.69</v>
       </c>
-      <c r="AF8" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.59</v>
+        <v>3.74</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.65</v>
+        <v>7.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.27</v>
+        <v>1.86</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U9" t="n">
-        <v>2.82</v>
+        <v>3.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.74</v>
+        <v>2.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="AM9" t="n">
         <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-      